--- a/Architecture_DayLight_CyberTrust/Daylight_CyberTrust_Architecture_Equipements_Zones.xlsx
+++ b/Architecture_DayLight_CyberTrust/Daylight_CyberTrust_Architecture_Equipements_Zones.xlsx
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t>Inter-VLAN vers MGMT/SERVERS</t>
+          <t>Inter-zones vers MGMT/SERVERS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="0">
